--- a/stories/arbres/ATOM-LAN.NOM.001-05.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Pauline et maman sont au jardin. Il y a un seau. Dedans, des cailloux. Maman dit : on va compter des objets. Pauline touche un caillou. Un. Elle en touche un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Pauline dit : cinq cailloux. Maman sourit. Elle dit le nombre. Cinq. Pauline pose les cailloux. Un. Deux. Trois. Quatre. Cinq. Les objets sont là. Pauline les compte. Le soleil chauffe le seau.</t>
+          <t>Pauline et maman sont au jardin. Il y a un seau. Dedans, des cailloux. On va compter des objets. Pauline touche un caillou. Un. Elle en touche un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Cinq cailloux. Maman sourit. Elle dit le nombre. Cinq. Pauline pose les cailloux. Un. Deux. Trois. Quatre. Cinq. Les objets sont là. Pauline les compte. Le soleil chauffe le seau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Pauline et maman sont au jardin. Il y a un seau. Dedans, des cailloux.
+maman|On va compter des objets.
+narrateur|Pauline touche un caillou. Un. Elle en touche un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq.
+enfant-f|Cinq cailloux. Maman sourit. Elle dit le nombre. Cinq.
+narrateur|Pauline pose les cailloux. Un. Deux. Trois. Quatre. Cinq. Les objets sont là. Pauline les compte. Le soleil chauffe le seau.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Pauline compte les cailloux. Combien y en a-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1659,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Pauline a compté des objets. Cinq cailloux. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,6 +1822,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range le seau. Pauline garde un caillou lisse.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,6 +1989,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1967,7 +2012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1984,6 +2029,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-05.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Pauline pose les cailloux. Un. Deux. Trois. Quatre. Cinq. Les objets sont là. Pauline les compte. Le soleil chauffe le seau.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Pauline compte les cailloux. Combien y en a-t-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1664,6 +1671,7 @@
           <t>narrateur|Pauline a compté des objets. Cinq cailloux. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1827,6 +1835,7 @@
           <t>narrateur|Maman range le seau. Pauline garde un caillou lisse.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1994,6 +2003,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2012,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2036,6 +2046,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2237,6 +2261,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.NOM.001-05.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pauline compte les cailloux</t>
+          <t>Mila compte les cailloux</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une flaque tremble près du seau. Mila touche les cailloux un à un. Elle dit cinq. Papa et maman écoutent.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Pauline et maman sont au jardin. Il y a un seau. Dedans, des cailloux. On va compter des objets. Pauline touche un caillou. Un. Elle en touche un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Cinq cailloux. Maman sourit. Elle dit le nombre. Cinq. Pauline pose les cailloux. Un. Deux. Trois. Quatre. Cinq. Les objets sont là. Pauline les compte. Le soleil chauffe le seau.</t>
+          <t>Une flaque tremble près du seau. Le ciel se voit dedans. Les bottes de Mila sont encore humides. Elles sentent la terre. Un seau gris repose sur la marche. Le métal est froid. Une feuille collée au seau. La feuille est jaune et molle. La gouttière finit de chanter. Mila, tu vois la flaque ? Oui, maman. Elle tremble. Le seau est là. Les cailloux sont propres. En ce moment, Mila s'approche. Dedans le seau, des cailloux. Ils sont ronds et gris. On compte des objets. On touche. On dit le nombre. Mila touche un caillou. Un. Elle en touche un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Cinq cailloux. Tu as dit le nombre. Cinq. Tu as compté des objets. Bravo, Mila. C'est du bon travail. Mila pose les cailloux. Un. Deux. Trois. Quatre. Cinq. Encore cinq. Tu dis le nombre ? Cinq. La flaque redevient calme. La feuille reste molle. On range le seau ? Oui, maman. Mila pose un caillou lisse. Le métal reste froid. Les objets sont là. On les a comptés. Une feuille jaune repose près du seau. Papa en pose d'autres. On compte aussi les feuilles ? Oui, papa. Mila touche une feuille. Une. Elle en touche une autre. Deux. Encore une. Trois. Trois feuilles. Tu dis le nombre. Trois. Bravo. La gouttière se tait. Les bottes restent humides.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,76 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Pauline et maman sont au jardin. Il y a un seau. Dedans, des cailloux.
-maman|On va compter des objets.
-narrateur|Pauline touche un caillou. Un. Elle en touche un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq.
-enfant-f|Cinq cailloux. Maman sourit. Elle dit le nombre. Cinq.
-narrateur|Pauline pose les cailloux. Un. Deux. Trois. Quatre. Cinq. Les objets sont là. Pauline les compte. Le soleil chauffe le seau.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une flaque tremble près du seau.
+narrateur|Le ciel se voit dedans.
+narrateur|Les bottes de Mila sont encore humides.
+narrateur|Elles sentent la terre.
+narrateur|Un seau gris repose sur la marche.
+narrateur|Le métal est froid.
+narrateur|Une feuille collée au seau.
+narrateur|La feuille est jaune et molle.
+narrateur|La gouttière finit de chanter.
+maman|Mila, tu vois la flaque ?
+enfant-f|Oui, maman.
+enfant-f|Elle tremble.
+papa|Le seau est là.
+maman|Les cailloux sont propres.
+narrateur|En ce moment, Mila s'approche.
+narrateur|Dedans le seau, des cailloux.
+narrateur|Ils sont ronds et gris.
+papa|On compte des objets.
+maman|On touche. On dit le nombre.
+narrateur|Mila touche un caillou.
+enfant-f|Un.
+narrateur|Elle en touche un autre.
+enfant-f|Deux.
+narrateur|Encore un.
+enfant-f|Trois.
+narrateur|Encore un.
+enfant-f|Quatre.
+narrateur|Encore un.
+enfant-f|Cinq.
+papa|Cinq cailloux.
+maman|Tu as dit le nombre.
+enfant-f|Cinq.
+papa|Tu as compté des objets.
+papa|Bravo, Mila.
+maman|C'est du bon travail.
+narrateur|Mila pose les cailloux.
+enfant-f|Un.
+enfant-f|Deux.
+enfant-f|Trois.
+enfant-f|Quatre.
+enfant-f|Cinq.
+maman|Encore cinq.
+papa|Tu dis le nombre ?
+enfant-f|Cinq.
+narrateur|La flaque redevient calme.
+narrateur|La feuille reste molle.
+maman|On range le seau ?
+enfant-f|Oui, maman.
+narrateur|Mila pose un caillou lisse.
+narrateur|Le métal reste froid.
+papa|Les objets sont là.
+maman|On les a comptés.
+narrateur|Une feuille jaune repose près du seau.
+narrateur|Papa en pose d'autres.
+papa|On compte aussi les feuilles ?
+enfant-f|Oui, papa.
+narrateur|Mila touche une feuille.
+enfant-f|Une.
+narrateur|Elle en touche une autre.
+enfant-f|Deux.
+narrateur|Encore une.
+enfant-f|Trois.
+maman|Trois feuilles.
+papa|Tu dis le nombre.
+enfant-f|Trois.
+maman|Bravo.
+narrateur|La gouttière se tait.
+narrateur|Les bottes restent humides.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1418,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Pauline compte les cailloux. Combien y en a-t-il ?</t>
+          <t>Mila compte les cailloux. Combien y en a-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,10 +1574,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Pauline compte les cailloux. Combien y en a-t-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Mila compte les cailloux.
+narrateur|Combien y en a-t-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,7 +1602,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Pauline a compté des objets. Cinq cailloux. Elle a dit le nombre.</t>
+          <t>Mila a compté des objets. Cinq cailloux. Elle a dit le nombre. Tu as dit cinq ? Oui, papa. Bravo, Mila. Tu as fait du bon travail. Le seau repose sur la marche. Il est encore un peu froid. Les cailloux sont à leur place ? Oui, papa. Un caillou lisse brille.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1668,10 +1742,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Pauline a compté des objets. Cinq cailloux. Elle a dit le nombre.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila a compté des objets.
+narrateur|Cinq cailloux.
+narrateur|Elle a dit le nombre.
+papa|Tu as dit cinq ?
+enfant-f|Oui, papa.
+maman|Bravo, Mila.
+maman|Tu as fait du bon travail.
+narrateur|Le seau repose sur la marche.
+narrateur|Il est encore un peu froid.
+papa|Les cailloux sont à leur place ?
+enfant-f|Oui, papa.
+narrateur|Un caillou lisse brille.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1696,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le seau. Pauline garde un caillou lisse.</t>
+          <t>Mila pose le seau. Je t'essuie les mains ? Oui, maman. Maman essuie tout doux. Le torchon est un peu rêche. Tu as fini de compter ? Oui, papa. Bravo. La flaque est calme. On rentre les bottes ? Oui. Ça sent encore la terre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1832,10 +1916,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range le seau. Pauline garde un caillou lisse.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Mila pose le seau.
+maman|Je t'essuie les mains ?
+enfant-f|Oui, maman.
+narrateur|Maman essuie tout doux.
+narrateur|Le torchon est un peu rêche.
+papa|Tu as fini de compter ?
+enfant-f|Oui, papa.
+papa|Bravo.
+narrateur|La flaque est calme.
+maman|On rentre les bottes ?
+enfant-f|Oui.
+narrateur|Ça sent encore la terre.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1860,7 +1954,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila tient un caillou lisse. Le seau reste sur la marche. Merci d'avoir compté. On touche. On dit le nombre. Oui. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2000,10 +2094,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Mila tient un caillou lisse.
+narrateur|Le seau reste sur la marche.
+maman|Merci d'avoir compté.
+papa|On touche. On dit le nombre.
+enfant-f|Oui.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2060,6 +2158,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-05.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-05.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mila compte les cailloux</t>
+          <t>Le seau mouillé de Victorina</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Une flaque tremble près du seau. Mila touche les cailloux un à un. Elle dit cinq. Papa et maman écoutent.</t>
+          <t>La terre sent encore la pluie. Victorina touche les cailloux du seau. Un. Deux. Trois. Quatre. Cinq. Elle dit le nombre.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une flaque tremble près du seau. Le ciel se voit dedans. Les bottes de Mila sont encore humides. Elles sentent la terre. Un seau gris repose sur la marche. Le métal est froid. Une feuille collée au seau. La feuille est jaune et molle. La gouttière finit de chanter. Mila, tu vois la flaque ? Oui, maman. Elle tremble. Le seau est là. Les cailloux sont propres. En ce moment, Mila s'approche. Dedans le seau, des cailloux. Ils sont ronds et gris. On compte des objets. On touche. On dit le nombre. Mila touche un caillou. Un. Elle en touche un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Cinq cailloux. Tu as dit le nombre. Cinq. Tu as compté des objets. Bravo, Mila. C'est du bon travail. Mila pose les cailloux. Un. Deux. Trois. Quatre. Cinq. Encore cinq. Tu dis le nombre ? Cinq. La flaque redevient calme. La feuille reste molle. On range le seau ? Oui, maman. Mila pose un caillou lisse. Le métal reste froid. Les objets sont là. On les a comptés. Une feuille jaune repose près du seau. Papa en pose d'autres. On compte aussi les feuilles ? Oui, papa. Mila touche une feuille. Une. Elle en touche une autre. Deux. Encore une. Trois. Trois feuilles. Tu dis le nombre. Trois. Bravo. La gouttière se tait. Les bottes restent humides.</t>
+          <t>La terre du jardin sent encore la pluie. Une flaque ronde brille. Des gouttes pendent aux feuilles. Un seau vert est mouillé. Il sent la terre. Un ver a laissé un trait lisse. Un oiseau secoue une branche. Le paillasson est encore mouillé. Une botte verte attend près de la porte. Tu as vu la flaque, Victorina ? Oui, maman. Elle brille. On reste près du seau. En ce moment, Victorina s'accroupit. Dedans le seau, des cailloux. Ils sont brillants et froids. On va compter des objets. Des cailloux. Des cailloux. Victorina touche un caillou. Il est lisse et froid. Un. Un. Elle en touche un autre. Deux. Deux. Encore un. Trois. Trois. Encore un. Quatre. Quatre. Encore un. Cinq. Cinq. Cinq cailloux. Tu as dit le nombre. Cinq. Bravo, Victorina. Tu as compté des objets. C'est du bon travail. Le soleil chauffe un peu le seau. On pose les cailloux ? Oui, maman. Victorina pose un caillou. Un. Elle en pose un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Les objets sont là. Tu les as comptés. Cinq. Oui. Tu as dit le nombre. La flaque tremble un peu. Ça sent la terre, hein ? Oui. La terre mouillée. Un oiseau secoue encore la branche. Une goutte tombe dans la flaque. Tu as fini de compter ? Oui, maman. Cinq. Bravo. Tu as compté des objets. Le seau vert brille un peu. La terre reste douce sous les doigts.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Pauline et maman sont au jardin. Il y a un seau. Dedans, des cailloux. Maman dit : on va &lt;emphasis level="moderate"&gt;compter&lt;/emphasis&gt; des objets. Pauline touche un caillou. Un. Elle en touche un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Pauline dit : cinq cailloux. Maman sourit. Elle dit le nombre. Cinq. Pauline pose les cailloux. Un. Deux. Trois. Quatre. Cinq. Les objets sont là. Pauline les compte. Le soleil chauffe le seau.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La terre du jardin sent encore la pluie. Une flaque ronde brille. Des gouttes pendent aux feuilles. Un seau vert est mouillé. Il sent la terre. Un ver a laissé un trait lisse. Un oiseau secoue une branche. Le paillasson est encore mouillé. Une botte verte attend près de la porte. Tu as vu la flaque, Victorina ? Oui, maman. Elle brille. On reste près du seau. En ce moment, Victorina s'accroupit. Dedans le seau, des cailloux. Ils sont brillants et froids. On va compter des objets. Des cailloux. Des cailloux. Victorina touche un caillou. Il est lisse et froid. Un. Un. Elle en touche un autre. Deux. Deux. Encore un. Trois. Trois. Encore un. Quatre. Quatre. Encore un. Cinq. Cinq. Cinq cailloux. Tu as dit le nombre. Cinq. Bravo, Victorina. Tu as compté des objets. C'est du bon travail. Le soleil chauffe un peu le seau. On pose les cailloux ? Oui, maman. Victorina pose un caillou. Un. Elle en pose un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Les objets sont là. Tu les as comptés. Cinq. Oui. Tu as dit le nombre. La flaque tremble un peu. Ça sent la terre, hein ? Oui. La terre mouillée. Un oiseau secoue encore la branche. Une goutte tombe dans la flaque. Tu as fini de compter ? Oui, maman. Cinq. Bravo. Tu as compté des objets. Le seau vert brille un peu. La terre reste douce sous les doigts.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1324,28 +1324,53 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Une flaque tremble près du seau.
-narrateur|Le ciel se voit dedans.
-narrateur|Les bottes de Mila sont encore humides.
-narrateur|Elles sentent la terre.
-narrateur|Un seau gris repose sur la marche.
-narrateur|Le métal est froid.
-narrateur|Une feuille collée au seau.
-narrateur|La feuille est jaune et molle.
-narrateur|La gouttière finit de chanter.
-maman|Mila, tu vois la flaque ?
+          <t>narrateur|La terre du jardin sent encore la pluie.
+narrateur|Une flaque ronde brille.
+narrateur|Des gouttes pendent aux feuilles.
+narrateur|Un seau vert est mouillé.
+narrateur|Il sent la terre.
+narrateur|Un ver a laissé un trait lisse.
+narrateur|Un oiseau secoue une branche.
+narrateur|Le paillasson est encore mouillé.
+narrateur|Une botte verte attend près de la porte.
+maman|Tu as vu la flaque, Victorina ?
 enfant-f|Oui, maman.
-enfant-f|Elle tremble.
-papa|Le seau est là.
-maman|Les cailloux sont propres.
-narrateur|En ce moment, Mila s'approche.
+enfant-f|Elle brille.
+maman|On reste près du seau.
+narrateur|En ce moment, Victorina s'accroupit.
 narrateur|Dedans le seau, des cailloux.
-narrateur|Ils sont ronds et gris.
-papa|On compte des objets.
-maman|On touche. On dit le nombre.
-narrateur|Mila touche un caillou.
+narrateur|Ils sont brillants et froids.
+maman|On va compter des objets.
+maman|Des cailloux.
+enfant-f|Des cailloux.
+narrateur|Victorina touche un caillou.
+narrateur|Il est lisse et froid.
+maman|Un.
 enfant-f|Un.
 narrateur|Elle en touche un autre.
+maman|Deux.
+enfant-f|Deux.
+narrateur|Encore un.
+maman|Trois.
+enfant-f|Trois.
+narrateur|Encore un.
+maman|Quatre.
+enfant-f|Quatre.
+narrateur|Encore un.
+maman|Cinq.
+enfant-f|Cinq.
+enfant-f|Cinq cailloux.
+maman|Tu as dit le nombre.
+maman|Cinq.
+maman|Bravo, Victorina.
+maman|Tu as compté des objets.
+maman|C'est du bon travail.
+narrateur|Le soleil chauffe un peu le seau.
+maman|On pose les cailloux ?
+enfant-f|Oui, maman.
+narrateur|Victorina pose un caillou.
+enfant-f|Un.
+narrateur|Elle en pose un autre.
 enfant-f|Deux.
 narrateur|Encore un.
 enfant-f|Trois.
@@ -1353,45 +1378,24 @@
 enfant-f|Quatre.
 narrateur|Encore un.
 enfant-f|Cinq.
-papa|Cinq cailloux.
+maman|Les objets sont là.
+maman|Tu les as comptés.
+enfant-f|Cinq.
+maman|Oui.
 maman|Tu as dit le nombre.
+narrateur|La flaque tremble un peu.
+maman|Ça sent la terre, hein ?
+enfant-f|Oui.
+enfant-f|La terre mouillée.
+narrateur|Un oiseau secoue encore la branche.
+narrateur|Une goutte tombe dans la flaque.
+maman|Tu as fini de compter ?
+enfant-f|Oui, maman.
 enfant-f|Cinq.
-papa|Tu as compté des objets.
-papa|Bravo, Mila.
-maman|C'est du bon travail.
-narrateur|Mila pose les cailloux.
-enfant-f|Un.
-enfant-f|Deux.
-enfant-f|Trois.
-enfant-f|Quatre.
-enfant-f|Cinq.
-maman|Encore cinq.
-papa|Tu dis le nombre ?
-enfant-f|Cinq.
-narrateur|La flaque redevient calme.
-narrateur|La feuille reste molle.
-maman|On range le seau ?
-enfant-f|Oui, maman.
-narrateur|Mila pose un caillou lisse.
-narrateur|Le métal reste froid.
-papa|Les objets sont là.
-maman|On les a comptés.
-narrateur|Une feuille jaune repose près du seau.
-narrateur|Papa en pose d'autres.
-papa|On compte aussi les feuilles ?
-enfant-f|Oui, papa.
-narrateur|Mila touche une feuille.
-enfant-f|Une.
-narrateur|Elle en touche une autre.
-enfant-f|Deux.
-narrateur|Encore une.
-enfant-f|Trois.
-maman|Trois feuilles.
-papa|Tu dis le nombre.
-enfant-f|Trois.
 maman|Bravo.
-narrateur|La gouttière se tait.
-narrateur|Les bottes restent humides.</t>
+maman|Tu as compté des objets.
+narrateur|Le seau vert brille un peu.
+narrateur|La terre reste douce sous les doigts.</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1422,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Mila compte les cailloux. Combien y en a-t-il ?</t>
+          <t>Victorina compte les cailloux. Combien y en a-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Pauline compte les cailloux. Combien y en a-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina compte les cailloux. Combien y en a-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1574,7 +1578,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Mila compte les cailloux.
+          <t>narrateur|Victorina compte les cailloux.
 narrateur|Combien y en a-t-il ?</t>
         </is>
       </c>
@@ -1602,12 +1606,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a compté des objets. Cinq cailloux. Elle a dit le nombre. Tu as dit cinq ? Oui, papa. Bravo, Mila. Tu as fait du bon travail. Le seau repose sur la marche. Il est encore un peu froid. Les cailloux sont à leur place ? Oui, papa. Un caillou lisse brille.</t>
+          <t>Victorina a compté des objets. Cinq cailloux. Elle a dit le nombre. Cinq. Bravo, Victorina. Cinq cailloux. Tu as fait du bon travail. Le seau vert reste mouillé. Les gouttes pendent encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Pauline a compté des objets. Cinq cailloux. Elle a dit le nombre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a compté des objets. Cinq cailloux. Elle a dit le nombre. Cinq. Bravo, Victorina. Cinq cailloux. Tu as fait du bon travail. Le seau vert reste mouillé. Les gouttes pendent encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1742,18 +1746,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Mila a compté des objets.
+          <t>narrateur|Victorina a compté des objets.
 narrateur|Cinq cailloux.
 narrateur|Elle a dit le nombre.
-papa|Tu as dit cinq ?
-enfant-f|Oui, papa.
-maman|Bravo, Mila.
+maman|Cinq.
+maman|Bravo, Victorina.
+enfant-f|Cinq cailloux.
 maman|Tu as fait du bon travail.
-narrateur|Le seau repose sur la marche.
-narrateur|Il est encore un peu froid.
-papa|Les cailloux sont à leur place ?
-enfant-f|Oui, papa.
-narrateur|Un caillou lisse brille.</t>
+narrateur|Le seau vert reste mouillé.
+narrateur|Les gouttes pendent encore.</t>
         </is>
       </c>
     </row>
@@ -1780,12 +1781,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Mila pose le seau. Je t'essuie les mains ? Oui, maman. Maman essuie tout doux. Le torchon est un peu rêche. Tu as fini de compter ? Oui, papa. Bravo. La flaque est calme. On rentre les bottes ? Oui. Ça sent encore la terre.</t>
+          <t>On range le seau ? Oui, maman. Maman range le seau. Victorina garde un caillou lisse. Il est doux, hein ? Oui. Il est lisse. Tu as fini de compter ? Oui, maman. Bravo. La flaque brille encore. La botte verte reste près de la porte. On rentre les pieds secs ? Oui, maman. Le seau sent encore la terre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maman range le seau. Pauline garde un caillou lisse.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On range le seau ? Oui, maman. Maman range le seau. Victorina garde un caillou lisse. Il est doux, hein ? Oui. Il est lisse. Tu as fini de compter ? Oui, maman. Bravo. La flaque brille encore. La botte verte reste près de la porte. On rentre les pieds secs ? Oui, maman. Le seau sent encore la terre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1916,18 +1917,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Mila pose le seau.
-maman|Je t'essuie les mains ?
+          <t>maman|On range le seau ?
 enfant-f|Oui, maman.
-narrateur|Maman essuie tout doux.
-narrateur|Le torchon est un peu rêche.
-papa|Tu as fini de compter ?
-enfant-f|Oui, papa.
-papa|Bravo.
-narrateur|La flaque est calme.
-maman|On rentre les bottes ?
+narrateur|Maman range le seau.
+narrateur|Victorina garde un caillou lisse.
+maman|Il est doux, hein ?
 enfant-f|Oui.
-narrateur|Ça sent encore la terre.</t>
+enfant-f|Il est lisse.
+maman|Tu as fini de compter ?
+enfant-f|Oui, maman.
+maman|Bravo.
+narrateur|La flaque brille encore.
+narrateur|La botte verte reste près de la porte.
+maman|On rentre les pieds secs ?
+enfant-f|Oui, maman.
+narrateur|Le seau sent encore la terre.</t>
         </is>
       </c>
     </row>
@@ -1954,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mila tient un caillou lisse. Le seau reste sur la marche. Merci d'avoir compté. On touche. On dit le nombre. Oui. L'histoire est finie.</t>
+          <t>Cinq cailloux. Tu as compté des objets. Tu as dit le nombre. Bravo, Victorina. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Cinq cailloux. Tu as compté des objets. Tu as dit le nombre. Bravo, Victorina. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2094,11 +2098,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Mila tient un caillou lisse.
-narrateur|Le seau reste sur la marche.
-maman|Merci d'avoir compté.
-papa|On touche. On dit le nombre.
-enfant-f|Oui.
+          <t>enfant-f|Cinq cailloux.
+maman|Tu as compté des objets.
+maman|Tu as dit le nombre.
+maman|Bravo, Victorina.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2120,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2165,6 +2168,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.NOM.001-05.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La terre du jardin sent encore la pluie. Une flaque ronde brille. Des gouttes pendent aux feuilles. Un seau vert est mouillé. Il sent la terre. Un ver a laissé un trait lisse. Un oiseau secoue une branche. Le paillasson est encore mouillé. Une botte verte attend près de la porte. Tu as vu la flaque, Victorina ? Oui, maman. Elle brille. On reste près du seau. En ce moment, Victorina s'accroupit. Dedans le seau, des cailloux. Ils sont brillants et froids. On va compter des objets. Des cailloux. Des cailloux. Victorina touche un caillou. Il est lisse et froid. Un. Un. Elle en touche un autre. Deux. Deux. Encore un. Trois. Trois. Encore un. Quatre. Quatre. Encore un. Cinq. Cinq. Cinq cailloux. Tu as dit le nombre. Cinq. Bravo, Victorina. Tu as compté des objets. C'est du bon travail. Le soleil chauffe un peu le seau. On pose les cailloux ? Oui, maman. Victorina pose un caillou. Un. Elle en pose un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Les objets sont là. Tu les as comptés. Cinq. Oui. Tu as dit le nombre. La flaque tremble un peu. Ça sent la terre, hein ? Oui. La terre mouillée. Un oiseau secoue encore la branche. Une goutte tombe dans la flaque. Tu as fini de compter ? Oui, maman. Cinq. Bravo. Tu as compté des objets. Le seau vert brille un peu. La terre reste douce sous les doigts.</t>
+          <t>La terre du jardin sent encore la pluie. Une flaque ronde brille. Des gouttes pendent aux feuilles. Un seau vert est mouillé. Il sent la terre. Un ver a laissé un trait lisse. Un oiseau secoue une branche. Le paillasson est encore mouillé. Une botte verte attend près de la porte. Tu as vu la flaque, Victorina ? Oui, maman. Elle brille. On reste près du seau. En ce moment, Victorina s'accroupit. Dedans le seau, des cailloux. Ils sont brillants et froids. On va compter des objets. Des cailloux. Des cailloux. Victorina touche un caillou. Il est lisse et froid. Un. Un. Elle en touche un autre. Deux. Deux. Encore un. Trois. Trois. Encore un. Quatre. Quatre. Encore un. Cinq. Cinq. Cinq cailloux. Tu as dit le nombre. Cinq. Bravo, Victorina. Tu as compté des objets. Le soleil chauffe un peu le seau. On pose les cailloux ? Oui, maman. Victorina pose un caillou. Un. Elle en pose un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Les objets sont là. Tu les as comptés. Cinq. Oui. Tu as dit le nombre. La flaque tremble un peu. Ça sent la terre, hein ? Oui. La terre mouillée. Un oiseau secoue encore la branche. Une goutte tombe dans la flaque. Tu as fini de compter ? Oui, maman. Cinq. Bravo. Tu as compté des objets. Le seau vert brille un peu. La terre reste douce sous les doigts.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La terre du jardin sent encore la pluie. Une flaque ronde brille. Des gouttes pendent aux feuilles. Un seau vert est mouillé. Il sent la terre. Un ver a laissé un trait lisse. Un oiseau secoue une branche. Le paillasson est encore mouillé. Une botte verte attend près de la porte. Tu as vu la flaque, Victorina ? Oui, maman. Elle brille. On reste près du seau. En ce moment, Victorina s'accroupit. Dedans le seau, des cailloux. Ils sont brillants et froids. On va compter des objets. Des cailloux. Des cailloux. Victorina touche un caillou. Il est lisse et froid. Un. Un. Elle en touche un autre. Deux. Deux. Encore un. Trois. Trois. Encore un. Quatre. Quatre. Encore un. Cinq. Cinq. Cinq cailloux. Tu as dit le nombre. Cinq. Bravo, Victorina. Tu as compté des objets. C'est du bon travail. Le soleil chauffe un peu le seau. On pose les cailloux ? Oui, maman. Victorina pose un caillou. Un. Elle en pose un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Les objets sont là. Tu les as comptés. Cinq. Oui. Tu as dit le nombre. La flaque tremble un peu. Ça sent la terre, hein ? Oui. La terre mouillée. Un oiseau secoue encore la branche. Une goutte tombe dans la flaque. Tu as fini de compter ? Oui, maman. Cinq. Bravo. Tu as compté des objets. Le seau vert brille un peu. La terre reste douce sous les doigts.</t>
+          <t>La terre du jardin sent encore la pluie. Une flaque ronde brille. Des gouttes pendent aux feuilles. Un seau vert est mouillé. Il sent la terre. Un ver a laissé un trait lisse. Un oiseau secoue une branche. Le paillasson est encore mouillé. Une botte verte attend près de la porte. Tu as vu la flaque, Victorina ? Oui, maman. Elle brille. On reste près du seau. En ce moment, Victorina s'accroupit. Dedans le seau, des cailloux. Ils sont brillants et froids. On va compter des objets. Des cailloux. Des cailloux. Victorina touche un caillou. Il est lisse et froid. Un. Un. Elle en touche un autre. Deux. Deux. Encore un. Trois. Trois. Encore un. Quatre. Quatre. Encore un. Cinq. Cinq. Cinq cailloux. Tu as dit le nombre. Cinq. Bravo, Victorina. Tu as compté des objets. Le soleil chauffe un peu le seau. On pose les cailloux ? Oui, maman. Victorina pose un caillou. Un. Elle en pose un autre. Deux. Encore un. Trois. Encore un. Quatre. Encore un. Cinq. Les objets sont là. Tu les as comptés. Cinq. Oui. Tu as dit le nombre. La flaque tremble un peu. Ça sent la terre, hein ? Oui. La terre mouillée. Un oiseau secoue encore la branche. Une goutte tombe dans la flaque. Tu as fini de compter ? Oui, maman. Cinq. Bravo. Tu as compté des objets. Le seau vert brille un peu. La terre reste douce sous les doigts.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1364,7 +1364,6 @@
 maman|Cinq.
 maman|Bravo, Victorina.
 maman|Tu as compté des objets.
-maman|C'est du bon travail.
 narrateur|Le soleil chauffe un peu le seau.
 maman|On pose les cailloux ?
 enfant-f|Oui, maman.
@@ -1606,12 +1605,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a compté des objets. Cinq cailloux. Elle a dit le nombre. Cinq. Bravo, Victorina. Cinq cailloux. Tu as fait du bon travail. Le seau vert reste mouillé. Les gouttes pendent encore.</t>
+          <t>Victorina a compté des objets. Cinq cailloux. Elle a dit le nombre. Cinq. Bravo, Victorina. Cinq cailloux. Le seau vert reste mouillé. Les gouttes pendent encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a compté des objets. Cinq cailloux. Elle a dit le nombre. Cinq. Bravo, Victorina. Cinq cailloux. Tu as fait du bon travail. Le seau vert reste mouillé. Les gouttes pendent encore.</t>
+          <t>Victorina a compté des objets. Cinq cailloux. Elle a dit le nombre. Cinq. Bravo, Victorina. Cinq cailloux. Le seau vert reste mouillé. Les gouttes pendent encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1752,7 +1751,6 @@
 maman|Cinq.
 maman|Bravo, Victorina.
 enfant-f|Cinq cailloux.
-maman|Tu as fait du bon travail.
 narrateur|Le seau vert reste mouillé.
 narrateur|Les gouttes pendent encore.</t>
         </is>
@@ -1958,12 +1956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Cinq cailloux. Tu as compté des objets. Tu as dit le nombre. Bravo, Victorina. L'histoire est finie.</t>
+          <t>Cinq cailloux. Tu as compté des objets. Tu as dit le nombre. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Cinq cailloux. Tu as compté des objets. Tu as dit le nombre. Bravo, Victorina. L'histoire est finie.</t>
+          <t>Cinq cailloux. Tu as compté des objets. Tu as dit le nombre. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2101,8 +2099,7 @@
           <t>enfant-f|Cinq cailloux.
 maman|Tu as compté des objets.
 maman|Tu as dit le nombre.
-maman|Bravo, Victorina.
-narrateur|L'histoire est finie.</t>
+maman|Bravo, Victorina.</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2173,6 +2170,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-LAN.NOM.001-05.xlsx
+++ b/stories/arbres/ATOM-LAN.NOM.001-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>jardin, après la pluie</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pauline, maman</t>
+          <t>Victorina, maman</t>
         </is>
       </c>
     </row>
